--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486475_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486475_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0225</v>
+        <v>4.3762</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2255</v>
+        <v>5.5176</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.203</v>
+        <v>-1.1414</v>
       </c>
       <c r="G2" t="n">
         <v>4.0619</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3445</v>
+        <v>-0.9908</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9349</v>
+        <v>-0.6429</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4096</v>
+        <v>-0.3479</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5066</v>
+        <v>3.4017</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2929</v>
+        <v>4.2497</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7863</v>
+        <v>-0.848</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0444</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0959</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0649</v>
+        <v>-0.1081</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1608</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>3.0202</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>D. SANADZE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4765</v>
+        <v>2.0942</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0489</v>
+        <v>1.2944</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4276</v>
+        <v>0.7998</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3769</v>
+        <v>3.0662</v>
       </c>
       <c r="H4" t="n">
-        <v>0.067</v>
+        <v>-0.0121</v>
       </c>
       <c r="I4" t="n">
-        <v>0.31</v>
+        <v>3.0783</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6463</v>
+        <v>2.9293</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1674</v>
+        <v>0.1737</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4789</v>
+        <v>2.7556</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2694</v>
+        <v>0.1369</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1004</v>
+        <v>-0.1858</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1689</v>
+        <v>0.3227</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6525</v>
+        <v>2.8276</v>
       </c>
       <c r="S4" t="n">
-        <v>0.447</v>
+        <v>-1.7773</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4026</v>
+        <v>-0.7426</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0445</v>
+        <v>-1.0347</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.9347</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SANADZE</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4071</v>
+        <v>1.253</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9771</v>
+        <v>0.8254</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4299</v>
+        <v>0.4276</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0662</v>
+        <v>0.3769</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0121</v>
+        <v>0.067</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0783</v>
+        <v>0.31</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9293</v>
+        <v>0.6463</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1737</v>
+        <v>0.1674</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7556</v>
+        <v>0.4789</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1369</v>
+        <v>-0.2694</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1858</v>
+        <v>-0.1004</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3227</v>
+        <v>-0.1689</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8276</v>
+        <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.4644</v>
+        <v>0.2235</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0599</v>
+        <v>0.1791</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.4046</v>
+        <v>0.0445</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9347</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2422</v>
+        <v>1.0286</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5829</v>
+        <v>0.8317</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6593</v>
+        <v>0.1969</v>
       </c>
       <c r="G6" t="n">
         <v>2.6998</v>
@@ -922,13 +922,13 @@
         <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2624</v>
+        <v>-1.476</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9349</v>
+        <v>-0.6862</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3275</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1952</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2512</v>
+        <v>0.4554</v>
       </c>
       <c r="E7" t="n">
-        <v>0.055</v>
+        <v>0.1667</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1962</v>
+        <v>0.2887</v>
       </c>
       <c r="G7" t="n">
         <v>0.3983</v>
@@ -1000,13 +1000,13 @@
         <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2123</v>
+        <v>-0.0081</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.274</v>
+        <v>-0.1622</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3698</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3967</v>
+        <v>-0.147</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.169</v>
+        <v>0.2347</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2276</v>
+        <v>-0.3817</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2819</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1148</v>
+        <v>0.1349</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.399</v>
+        <v>0.0048</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2842</v>
+        <v>0.1301</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7314000000000001</v>
+        <v>-0.8873</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0567</v>
+        <v>-0.3667</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6747</v>
+        <v>-0.5206</v>
       </c>
       <c r="G9" t="n">
         <v>1.2254</v>
@@ -1156,13 +1156,13 @@
         <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1542</v>
+        <v>-1.3101</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0529</v>
+        <v>-0.3629</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1014</v>
+        <v>-0.9472</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8902</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9557</v>
+        <v>-1.8311</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0361</v>
+        <v>-1.184</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9918</v>
+        <v>-0.6472</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1878</v>
+        <v>-2.0023</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6508</v>
+        <v>-1.8732</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.463</v>
+        <v>-0.1291</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7776</v>
+        <v>-0.367</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9671999999999999</v>
+        <v>-1.1918</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1896</v>
+        <v>0.8248</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5898</v>
+        <v>-1.6353</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3164</v>
+        <v>-0.6814</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2733</v>
+        <v>-0.9539</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R10" t="n">
-        <v>0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="S10" t="n">
-        <v>0.334</v>
+        <v>-0.8289</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3461</v>
+        <v>-0.2944</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0121</v>
+        <v>-0.5345</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.2599</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W10" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-2.2599</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6309</v>
+        <v>-2.21</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.768</v>
+        <v>-0.1874</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8629</v>
+        <v>-2.0227</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0023</v>
+        <v>0.1878</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8732</v>
+        <v>0.6508</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1291</v>
+        <v>-0.463</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.367</v>
+        <v>0.7776</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1918</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8248</v>
+        <v>-0.1896</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6353</v>
+        <v>-0.5898</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6814</v>
+        <v>-0.3164</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9539</v>
+        <v>-0.2733</v>
       </c>
       <c r="P11" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6287</v>
+        <v>0.0796</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8784</v>
+        <v>0.1226</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7502</v>
+        <v>-0.043</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5649999999999999</v>
+        <v>-2.2599</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7034</v>
+        <v>-6.0181</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9964</v>
+        <v>-6.1262</v>
       </c>
       <c r="F12" t="n">
-        <v>0.293</v>
+        <v>0.1081</v>
       </c>
       <c r="G12" t="n">
         <v>-6.0379</v>
@@ -1390,13 +1390,13 @@
         <v>2.8276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9933</v>
+        <v>-1.308</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4638</v>
+        <v>-0.5936</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5295</v>
+        <v>-0.7144</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4997</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4879999999999978</v>
+        <v>1.515600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>4.228299999999998</v>
+        <v>5.2559</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.7403</v>
+        <v>-3.7405</v>
       </c>
       <c r="G13" t="n">
         <v>3.649799999999998</v>
@@ -1450,7 +1450,7 @@
         <v>4.9687</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.9897</v>
+        <v>-5.989700000000001</v>
       </c>
       <c r="N13" t="n">
         <v>-3.2561</v>
@@ -1468,13 +1468,13 @@
         <v>18.488</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.297700000000001</v>
+        <v>-7.2702</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.314</v>
+        <v>-3.2864</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.9838</v>
+        <v>-3.9837</v>
       </c>
       <c r="V13" t="n">
         <v>-3.5643</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4972</v>
+        <v>5.0316</v>
       </c>
       <c r="E14" t="n">
-        <v>4.866</v>
+        <v>5.3131</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3688</v>
+        <v>-0.2815</v>
       </c>
       <c r="G14" t="n">
         <v>2.1534</v>
@@ -1546,13 +1546,13 @@
         <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3511</v>
+        <v>0.1833</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7294</v>
+        <v>-0.2824</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3783</v>
+        <v>0.4656</v>
       </c>
       <c r="V14" t="n">
         <v>2.2599</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ALDERETE DIAZ</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9015</v>
+        <v>2.4737</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5426</v>
+        <v>1.1231</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3589</v>
+        <v>1.3506</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2379</v>
+        <v>1.3871</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4347</v>
+        <v>0.9002</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6725</v>
+        <v>0.4869</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7286</v>
+        <v>1.9443</v>
       </c>
       <c r="K15" t="n">
-        <v>0.073</v>
+        <v>1.1195</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.8016</v>
+        <v>0.8248</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4907</v>
+        <v>-0.5572</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3617</v>
+        <v>-0.2193</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1291</v>
+        <v>-0.3379</v>
       </c>
       <c r="P15" t="n">
-        <v>0.435</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>2.8996</v>
+        <v>1.6091</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2712</v>
+        <v>0.5936</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6284</v>
+        <v>1.0154</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X15" t="n">
         <v>-0.1952</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. YU</t>
+          <t>D. ALDERETE DIAZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9858</v>
+        <v>2.1629</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7563</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2296</v>
+        <v>1.6261</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.4608</v>
+        <v>-0.2379</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.5516</v>
+        <v>0.4347</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.6725</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.341</v>
+        <v>-0.7286</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.0678</v>
+        <v>0.073</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7267</v>
+        <v>-0.8016</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1197</v>
+        <v>0.4907</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4838</v>
+        <v>0.3617</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6359</v>
+        <v>0.1291</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5792</v>
+        <v>2.1609</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2522</v>
+        <v>1.2654</v>
       </c>
       <c r="U16" t="n">
-        <v>1.327</v>
+        <v>0.8956</v>
       </c>
       <c r="V16" t="n">
-        <v>3.3899</v>
+        <v>-0.1952</v>
       </c>
       <c r="W16" t="n">
-        <v>3.0202</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7108</v>
+        <v>1.9831</v>
       </c>
       <c r="E17" t="n">
         <v>2.1848</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.474</v>
+        <v>-0.2017</v>
       </c>
       <c r="G17" t="n">
         <v>0.1061</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2997</v>
+        <v>0.572</v>
       </c>
       <c r="T17" t="n">
         <v>0.1406</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1591</v>
+        <v>0.4314</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>J. YU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1352</v>
+        <v>1.201</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4526</v>
+        <v>0.1975</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6827</v>
+        <v>1.0036</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3871</v>
+        <v>-2.4608</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9002</v>
+        <v>-2.5516</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4869</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9443</v>
+        <v>-1.341</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1195</v>
+        <v>-2.0678</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8248</v>
+        <v>0.7267</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5572</v>
+        <v>-1.1197</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2193</v>
+        <v>-0.4838</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3379</v>
+        <v>-0.6359</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0875</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2706</v>
+        <v>1.7944</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0769</v>
+        <v>0.6934</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3475</v>
+        <v>1.101</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5649999999999999</v>
+        <v>3.3899</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7602</v>
+        <v>3.0202</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5891</v>
+        <v>-0.5306</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5841</v>
+        <v>0.1423</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1732</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3872</v>
+        <v>1.1511</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3832</v>
+        <v>0.0881</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.004</v>
+        <v>1.063</v>
       </c>
       <c r="J19" t="n">
-        <v>0.401</v>
+        <v>2.5553</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5141</v>
+        <v>0.9855</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1131</v>
+        <v>1.5698</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7882</v>
+        <v>-1.4042</v>
       </c>
       <c r="N19" t="n">
         <v>-0.8974</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1091</v>
+        <v>-0.5068</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5583</v>
+        <v>-0.0291</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1406</v>
+        <v>-0.2379</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4177</v>
+        <v>0.2088</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.7602</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8902</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0084</v>
+        <v>-0.7869</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3047</v>
+        <v>0.3605</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7037</v>
+        <v>-1.1475</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1511</v>
+        <v>-0.3872</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0881</v>
+        <v>-0.3832</v>
       </c>
       <c r="I20" t="n">
-        <v>1.063</v>
+        <v>-0.004</v>
       </c>
       <c r="J20" t="n">
-        <v>2.5553</v>
+        <v>0.401</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9855</v>
+        <v>0.5141</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5698</v>
+        <v>-0.1131</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4042</v>
+        <v>-0.7882</v>
       </c>
       <c r="N20" t="n">
         <v>-0.8974</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5068</v>
+        <v>0.1091</v>
       </c>
       <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-1.0875</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.507</v>
+        <v>0.3605</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.0829</v>
       </c>
       <c r="U20" t="n">
-        <v>0.178</v>
+        <v>0.4434</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7602</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. VAN OOSTRUM</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6396</v>
+        <v>-2.6868</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9989</v>
+        <v>-2.8556</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6407</v>
+        <v>0.1688</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3192</v>
+        <v>-2.9338</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3558</v>
+        <v>0.4226</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.675</v>
+        <v>-3.3564</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1509</v>
+        <v>-1.7941</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1862</v>
+        <v>0.4594</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3371</v>
+        <v>-2.2535</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1683</v>
+        <v>-1.1397</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8304</v>
+        <v>-0.0368</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3379</v>
+        <v>-1.1029</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.305</v>
+        <v>-3.4801</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>-4.3501</v>
       </c>
       <c r="R21" t="n">
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0154</v>
+        <v>2.0321</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1971</v>
+        <v>1.0287</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2125</v>
+        <v>1.0034</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="W21" t="n">
-        <v>1.13</v>
+        <v>2.2599</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>D. VAN OOSTRUM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0851</v>
+        <v>-2.7642</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0791</v>
+        <v>-1.3342</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.006</v>
+        <v>-1.4301</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9338</v>
+        <v>-1.3192</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4226</v>
+        <v>0.3558</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3564</v>
+        <v>-1.675</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7941</v>
+        <v>-0.1509</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4594</v>
+        <v>1.1862</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.2535</v>
+        <v>-1.3371</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1397</v>
+        <v>-1.1683</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0368</v>
+        <v>-0.8304</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1029</v>
+        <v>-0.3379</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.4801</v>
+        <v>-1.305</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.3501</v>
+        <v>-2.1751</v>
       </c>
       <c r="R22" t="n">
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>1.6338</v>
+        <v>-0.14</v>
       </c>
       <c r="T22" t="n">
-        <v>0.8051</v>
+        <v>-0.1382</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8287</v>
+        <v>-0.0018</v>
       </c>
       <c r="V22" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.2599</v>
+        <v>1.13</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3963</v>
+        <v>-4.3365</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2631</v>
+        <v>-1.9278</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.1332</v>
+        <v>-2.4087</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1087</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0.93</v>
+        <v>1.9897</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6682</v>
+        <v>1.0034</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2618</v>
+        <v>0.9863</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8249</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4880000000000013</v>
+        <v>1.747299999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>3.7406</v>
+        <v>3.740499999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.228400000000001</v>
+        <v>-1.9933</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.6499</v>
+        <v>-3.649900000000001</v>
       </c>
       <c r="H24" t="n">
         <v>-1.4147</v>
@@ -2299,7 +2299,7 @@
         <v>-2.2352</v>
       </c>
       <c r="J24" t="n">
-        <v>5.989699999999998</v>
+        <v>5.9897</v>
       </c>
       <c r="K24" t="n">
         <v>3.2561</v>
@@ -2311,13 +2311,13 @@
         <v>-9.6395</v>
       </c>
       <c r="N24" t="n">
-        <v>-4.671</v>
+        <v>-4.670999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>-4.9687</v>
       </c>
       <c r="P24" t="n">
-        <v>-8.700200000000001</v>
+        <v>-8.700199999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-18.4881</v>
@@ -2326,13 +2326,13 @@
         <v>9.787499999999998</v>
       </c>
       <c r="S24" t="n">
-        <v>8.297700000000001</v>
+        <v>10.5329</v>
       </c>
       <c r="T24" t="n">
         <v>3.9837</v>
       </c>
       <c r="U24" t="n">
-        <v>4.314</v>
+        <v>6.5491</v>
       </c>
       <c r="V24" t="n">
         <v>3.5645</v>
